--- a/Result/profitability/3455.xlsx
+++ b/Result/profitability/3455.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7825</v>
+        <v>0.75125</v>
       </c>
       <c r="N2" t="n">
-        <v>51.7375</v>
+        <v>52.315</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.79</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8025</v>
+        <v>0.4275</v>
       </c>
       <c r="N3" t="n">
-        <v>49.3575</v>
+        <v>49.12625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44375</v>
+        <v>0.4825</v>
       </c>
       <c r="N4" t="n">
-        <v>46.9025</v>
+        <v>47.7875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.42875</v>
+        <v>0.6525</v>
       </c>
       <c r="N5" t="n">
-        <v>45.77124999999999</v>
+        <v>46.785</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.60875</v>
+        <v>0.32</v>
       </c>
       <c r="N6" t="n">
-        <v>42.73</v>
+        <v>42.52625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.18625</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>38.92874999999999</v>
+        <v>39.5225</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.025</v>
+        <v>0.17375</v>
       </c>
       <c r="N8" t="n">
-        <v>36.0125</v>
+        <v>36.42875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>356</v>
+      </c>
+      <c r="D75" t="n">
+        <v>150</v>
+      </c>
+      <c r="E75" t="n">
+        <v>206</v>
+      </c>
+      <c r="F75" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>23</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N75" t="n">
+        <v>54.81875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.469135802469136</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.329999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06105610561056096</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.269503546099291</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1629823151125402</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
